--- a/raw_data/characters_2026-2027.xlsx
+++ b/raw_data/characters_2026-2027.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Programming\pawapuro_combo_planner\raw_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6ABA37B3-D3B0-44B6-A09C-6C1178417774}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E72408E3-5F6D-45B0-AC9B-2BD2923CB323}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28898" yWindow="-98" windowWidth="28996" windowHeight="15675" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1711,10 +1711,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1999,9 +1999,7 @@
       <c r="B2" s="12" t="s">
         <v>289</v>
       </c>
-      <c r="C2" s="12">
-        <v>1</v>
-      </c>
+      <c r="C2" s="12"/>
       <c r="I2" s="1" t="s">
         <v>459</v>
       </c>
@@ -3626,7 +3624,7 @@
       <c r="C110" s="15" t="s">
         <v>327</v>
       </c>
-      <c r="D110" s="19"/>
+      <c r="D110" s="18"/>
       <c r="E110" s="17"/>
       <c r="F110" s="17"/>
       <c r="G110" s="17"/>
@@ -4928,7 +4926,7 @@
       <c r="C206" s="14" t="s">
         <v>358</v>
       </c>
-      <c r="D206" s="18"/>
+      <c r="D206" s="19"/>
       <c r="E206" s="17"/>
       <c r="F206" s="17"/>
       <c r="G206" s="17"/>
@@ -5052,7 +5050,7 @@
       <c r="C216" s="14" t="s">
         <v>359</v>
       </c>
-      <c r="D216" s="18"/>
+      <c r="D216" s="19"/>
       <c r="E216" s="17"/>
       <c r="F216" s="17"/>
       <c r="G216" s="17"/>
@@ -8272,46 +8270,6 @@
     </row>
   </sheetData>
   <mergeCells count="50">
-    <mergeCell ref="G1:H1"/>
-    <mergeCell ref="D54:N54"/>
-    <mergeCell ref="D57:N57"/>
-    <mergeCell ref="D58:N58"/>
-    <mergeCell ref="D100:Q100"/>
-    <mergeCell ref="D103:Q103"/>
-    <mergeCell ref="D72:N72"/>
-    <mergeCell ref="D75:T75"/>
-    <mergeCell ref="D59:N59"/>
-    <mergeCell ref="D62:N62"/>
-    <mergeCell ref="D67:N67"/>
-    <mergeCell ref="D145:Q145"/>
-    <mergeCell ref="D151:Q151"/>
-    <mergeCell ref="D119:Q119"/>
-    <mergeCell ref="D110:Q110"/>
-    <mergeCell ref="D115:Q115"/>
-    <mergeCell ref="D163:Q163"/>
-    <mergeCell ref="D167:Q167"/>
-    <mergeCell ref="D171:Q171"/>
-    <mergeCell ref="D155:Q155"/>
-    <mergeCell ref="D159:Q159"/>
-    <mergeCell ref="D216:Q216"/>
-    <mergeCell ref="D221:Q221"/>
-    <mergeCell ref="D206:Q206"/>
-    <mergeCell ref="D199:Q199"/>
-    <mergeCell ref="D192:Q192"/>
-    <mergeCell ref="D193:Q193"/>
-    <mergeCell ref="D194:Q194"/>
-    <mergeCell ref="D265:Q265"/>
-    <mergeCell ref="D233:Q233"/>
-    <mergeCell ref="D239:Q239"/>
-    <mergeCell ref="D225:Q225"/>
-    <mergeCell ref="D226:Q226"/>
-    <mergeCell ref="D227:Q227"/>
-    <mergeCell ref="D291:Q291"/>
-    <mergeCell ref="D295:Q295"/>
-    <mergeCell ref="D282:Q282"/>
-    <mergeCell ref="D286:Q286"/>
-    <mergeCell ref="D275:Q275"/>
-    <mergeCell ref="D277:Q277"/>
     <mergeCell ref="D369:H369"/>
     <mergeCell ref="D336:L336"/>
     <mergeCell ref="D337:L337"/>
@@ -8322,6 +8280,46 @@
     <mergeCell ref="D355:L355"/>
     <mergeCell ref="D357:L357"/>
     <mergeCell ref="D344:L344"/>
+    <mergeCell ref="D291:Q291"/>
+    <mergeCell ref="D295:Q295"/>
+    <mergeCell ref="D282:Q282"/>
+    <mergeCell ref="D286:Q286"/>
+    <mergeCell ref="D275:Q275"/>
+    <mergeCell ref="D277:Q277"/>
+    <mergeCell ref="D265:Q265"/>
+    <mergeCell ref="D233:Q233"/>
+    <mergeCell ref="D239:Q239"/>
+    <mergeCell ref="D225:Q225"/>
+    <mergeCell ref="D226:Q226"/>
+    <mergeCell ref="D227:Q227"/>
+    <mergeCell ref="D216:Q216"/>
+    <mergeCell ref="D221:Q221"/>
+    <mergeCell ref="D206:Q206"/>
+    <mergeCell ref="D199:Q199"/>
+    <mergeCell ref="D192:Q192"/>
+    <mergeCell ref="D193:Q193"/>
+    <mergeCell ref="D194:Q194"/>
+    <mergeCell ref="D163:Q163"/>
+    <mergeCell ref="D167:Q167"/>
+    <mergeCell ref="D171:Q171"/>
+    <mergeCell ref="D155:Q155"/>
+    <mergeCell ref="D159:Q159"/>
+    <mergeCell ref="D145:Q145"/>
+    <mergeCell ref="D151:Q151"/>
+    <mergeCell ref="D119:Q119"/>
+    <mergeCell ref="D110:Q110"/>
+    <mergeCell ref="D115:Q115"/>
+    <mergeCell ref="D103:Q103"/>
+    <mergeCell ref="D72:N72"/>
+    <mergeCell ref="D75:T75"/>
+    <mergeCell ref="D59:N59"/>
+    <mergeCell ref="D62:N62"/>
+    <mergeCell ref="D67:N67"/>
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="D54:N54"/>
+    <mergeCell ref="D57:N57"/>
+    <mergeCell ref="D58:N58"/>
+    <mergeCell ref="D100:Q100"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape" r:id="rId1"/>
